--- a/db-testing-tool/data/taxlot/DRD_Open_Tax_Lots_non_bkr_Fact (2).xlsx
+++ b/db-testing-tool/data/taxlot/DRD_Open_Tax_Lots_non_bkr_Fact (2).xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96330A85-761B-411A-8F5A-6DC41BEA9494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECFE4B4-A5A4-43F1-8CE2-C6C976A4687B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-46188" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table-View" sheetId="13" r:id="rId1"/>
@@ -37,6 +37,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -44,33 +47,58 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={A24A2D70-ED4E-44AB-B5CC-4CE7AFC2F48A}</author>
-    <author>tc={4AA4CE10-73FE-4646-8C7E-C1F0E2BF5E63}</author>
-    <author>tc={B5E08E26-35FA-412F-821B-340A9235FFC8}</author>
+    <author>Author</author>
   </authors>
   <commentList>
     <comment ref="A5" authorId="0" shapeId="0" xr:uid="{A24A2D70-ED4E-44AB-B5CC-4CE7AFC2F48A}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     No "&amp;" in Business Definition</t>
+        </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="1" shapeId="0" xr:uid="{4AA4CE10-73FE-4646-8C7E-C1F0E2BF5E63}">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{4AA4CE10-73FE-4646-8C7E-C1F0E2BF5E63}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     No spaces or any other format and No BYTE or CHAR please</t>
+        </r>
       </text>
     </comment>
-    <comment ref="H9" authorId="2" shapeId="0" xr:uid="{B5E08E26-35FA-412F-821B-340A9235FFC8}">
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{B5E08E26-35FA-412F-821B-340A9235FFC8}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     No "&amp;" in Business Definition</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -554,13 +582,6 @@
     <t>SBC_ASOF_ADJ_COST_AMT</t>
   </si>
   <si>
-    <t>ADJ_COST,
-case when (CCY_CODE ='USD' or (EXG_RATE is NULL OR EXG_RATE = 0)) THEN ADJ_COST
-ELSE 
-    ADJ_COST * EXG_RATE
-END SBC_ADJ_COST</t>
-  </si>
-  <si>
     <t>Currency Code</t>
   </si>
   <si>
@@ -649,13 +670,6 @@
   </si>
   <si>
     <t>SBC_ASOF_FAIR_MKT_VAL_AMT</t>
-  </si>
-  <si>
-    <t>FMV FAIR_MKT_VAL_OF_GIFT_OR_INHTN,
-case when (CCY_CODE ='USD' or (EXG_RATE is NULL OR EXG_RATE = 0)) THEN FMV
-ELSE 
-    FMV * EXG_RATE
-END SBC_FAIR_MKT_VAL</t>
   </si>
   <si>
     <t>Gift Date</t>
@@ -762,13 +776,6 @@
     <t>SBC_OPN_PRC_FCTR</t>
   </si>
   <si>
-    <t>OPN_FCTR OPN_PRC_FCTR,
-case when (CCY_CODE ='USD' or (EXG_RATE is NULL OR EXG_RATE = 0)) THEN OPN_FCTR
-ELSE 
-    OPN_FCTR * EXG_RATE
-END SBC_OPN_PRC_FCTR</t>
-  </si>
-  <si>
     <t>Open Transaction Event Type</t>
   </si>
   <si>
@@ -803,13 +810,6 @@
     <t>NML_ASOF_CRN_COST_AMT</t>
   </si>
   <si>
-    <t>ORIG_COST COST_AMT,
-case when (CCY_CODE ='USD' or (EXG_RATE is NULL OR EXG_RATE = 0)) THEN ORIG_COST
-ELSE 
-    ORIG_COST * EXG_RATE
-END SBC_COST_AMT</t>
-  </si>
-  <si>
     <t>Original Event Type</t>
   </si>
   <si>
@@ -841,13 +841,6 @@
     <t>SBC_ORIG_PRC</t>
   </si>
   <si>
-    <t>ORIG_PRC,
-case when (CCY_CODE ='USD' or (EXG_RATE is NULL OR EXG_RATE = 0)) THEN ORIG_PRC
-ELSE 
-    ORIG_PRC * EXG_RATE
-END SBC_ORIG_PRC</t>
-  </si>
-  <si>
     <t>Original Proceed</t>
   </si>
   <si>
@@ -859,13 +852,6 @@
   </si>
   <si>
     <t>SBC_ORIG_PROCD_AMT</t>
-  </si>
-  <si>
-    <t>ORIG_PROCD,
-case when (CCY_CODE ='USD' or (EXG_RATE is NULL OR EXG_RATE = 0)) THEN ORIG_PROCD
-ELSE 
-    ORIG_PROCD * EXG_RATE
-END SBC_ORIG_PROCD</t>
   </si>
   <si>
     <t>Original Transaction Type Code</t>
@@ -994,13 +980,6 @@
   </si>
   <si>
     <t>SBC_OPN_PER_UC_AMT</t>
-  </si>
-  <si>
-    <t>UC,
-case when (CCY_CODE ='USD' or (EXG_RATE is NULL OR EXG_RATE = 0)) THEN UC
-ELSE 
-    UC * EXG_RATE
-END SBC_UC</t>
   </si>
   <si>
     <t>System Base Currency Unit Cost</t>
@@ -2724,6 +2703,55 @@
   </si>
   <si>
     <t>MAXIT Source TAXLOT_DTL_OPN.ZERO_BSS_IND RJT Source: TAX_LOT_OPN_MSTR.ZERO_BSS_IND_F</t>
+  </si>
+  <si>
+    <t>ADJ_COST,
+case when (CCY_CODE ='USD' or (SBC_EXG_RATE is NULL OR SBC_EXG_RATE = 0)) THEN ADJ_COST
+ELSE 
+    ADJ_COST * SBC_EXG_RATE
+END SBC_ADJ_COST</t>
+  </si>
+  <si>
+    <t>FMV FAIR_MKT_VAL_OF_GIFT_OR_INHTN,
+case when (CCY_CODE ='USD' or (SBC_EXG_RATE is NULL OR SBC_EXG_RATE = 0)) THEN FMV
+ELSE 
+    FMV * SBC_EXG_RATE
+END SBC_FAIR_MKT_VAL</t>
+  </si>
+  <si>
+    <t>OPN_FCTR OPN_PRC_FCTR,
+case when (CCY_CODE ='USD' or (SBC_EXG_RATE is NULL OR SBC_EXG_RATE = 0)) THEN OPN_FCTR
+ELSE 
+    OPN_FCTR * SBC_EXG_RATE
+END SBC_OPN_PRC_FCTR</t>
+  </si>
+  <si>
+    <t>ORIG_COST COST_AMT,
+case when (CCY_CODE ='USD' or (SBC_EXG_RATE is NULL OR SBC_EXG_RATE = 0)) THEN ORIG_COST
+ELSE 
+    ORIG_COST * SBC_EXG_RATE
+END SBC_COST_AMT</t>
+  </si>
+  <si>
+    <t>ORIG_PRC,
+case when (CCY_CODE ='USD' or (SBC_EXG_RATE is NULL OR SBC_EXG_RATE = 0)) THEN ORIG_PRC
+ELSE 
+    ORIG_PRC * SBC_EXG_RATE
+END SBC_ORIG_PRC</t>
+  </si>
+  <si>
+    <t>ORIG_PROCD,
+case when (CCY_CODE ='USD' or (SBC_EXG_RATE is NULL OR SBC_EXG_RATE = 0)) THEN ORIG_PROCD
+ELSE 
+    ORIG_PROCD * SBC_EXG_RATE
+END SBC_ORIG_PROCD</t>
+  </si>
+  <si>
+    <t>UC,
+case when (CCY_CODE ='USD' or (SBC_EXG_RATE is NULL OR SBC_EXG_RATE = 0)) THEN UC
+ELSE 
+    UC * SBC_EXG_RATE
+END SBC_UC</t>
   </si>
 </sst>
 </file>
@@ -16016,7 +16044,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3FCE14-916F-44E5-ADDA-A49F8526702E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AA140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16375,7 +16402,7 @@
       </c>
       <c r="AA9"/>
     </row>
-    <row r="10" spans="1:27" hidden="1">
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -16437,7 +16464,7 @@
       <c r="Y10" s="19"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:27" ht="45" hidden="1">
+    <row r="11" spans="1:27" ht="45">
       <c r="A11" s="21" t="s">
         <v>45</v>
       </c>
@@ -16511,7 +16538,7 @@
       </c>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" spans="1:27" ht="66" hidden="1" customHeight="1">
+    <row r="12" spans="1:27" ht="66" customHeight="1">
       <c r="A12" s="21" t="s">
         <v>54</v>
       </c>
@@ -16583,7 +16610,7 @@
       <c r="Y12" s="19"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" spans="1:27" ht="50.25" hidden="1" customHeight="1">
+    <row r="13" spans="1:27" ht="50.25" customHeight="1">
       <c r="A13" s="21" t="s">
         <v>60</v>
       </c>
@@ -16658,7 +16685,7 @@
       </c>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:27" ht="33.75" hidden="1" customHeight="1">
+    <row r="14" spans="1:27" ht="33.75" customHeight="1">
       <c r="A14" s="21" t="s">
         <v>66</v>
       </c>
@@ -16731,7 +16758,7 @@
       <c r="Y14" s="19"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:27" ht="117" hidden="1" customHeight="1">
+    <row r="15" spans="1:27" ht="117" customHeight="1">
       <c r="A15" s="21" t="s">
         <v>69</v>
       </c>
@@ -16809,7 +16836,7 @@
       <c r="Y15" s="19"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:27" ht="45" hidden="1">
+    <row r="16" spans="1:27" ht="45">
       <c r="A16" s="21" t="s">
         <v>75</v>
       </c>
@@ -16881,7 +16908,7 @@
       <c r="Y16" s="19"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" ht="45" hidden="1">
+    <row r="17" spans="1:26" ht="45">
       <c r="A17" s="21" t="s">
         <v>80</v>
       </c>
@@ -16953,7 +16980,7 @@
       <c r="Y17" s="19"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18" spans="1:26" ht="30" hidden="1">
+    <row r="18" spans="1:26" ht="30">
       <c r="A18" s="21" t="s">
         <v>83</v>
       </c>
@@ -17024,7 +17051,7 @@
       <c r="Y18" s="19"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19" spans="1:26" ht="45" hidden="1">
+    <row r="19" spans="1:26" ht="45">
       <c r="A19" s="21" t="s">
         <v>86</v>
       </c>
@@ -17096,7 +17123,7 @@
       <c r="Y19" s="19"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20" spans="1:26" ht="45" hidden="1">
+    <row r="20" spans="1:26" ht="45">
       <c r="A20" s="21" t="s">
         <v>89</v>
       </c>
@@ -17168,7 +17195,7 @@
       <c r="Y20" s="19"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" ht="60" hidden="1">
+    <row r="21" spans="1:26" ht="60">
       <c r="A21" s="21" t="s">
         <v>95</v>
       </c>
@@ -17241,7 +17268,7 @@
       <c r="Y21" s="19"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" spans="1:26" s="39" customFormat="1" ht="90" hidden="1">
+    <row r="22" spans="1:26" s="39" customFormat="1" ht="90">
       <c r="A22" s="21" t="s">
         <v>99</v>
       </c>
@@ -17316,7 +17343,7 @@
       </c>
       <c r="Z22" s="24"/>
     </row>
-    <row r="23" spans="1:26" ht="75" hidden="1">
+    <row r="23" spans="1:26" ht="75">
       <c r="A23" s="21" t="s">
         <v>106</v>
       </c>
@@ -17390,7 +17417,7 @@
       <c r="Y23" s="19"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" spans="1:26" ht="61.5" hidden="1" customHeight="1">
+    <row r="24" spans="1:26" ht="61.5" customHeight="1">
       <c r="A24" s="21" t="s">
         <v>109</v>
       </c>
@@ -17460,33 +17487,33 @@
       <c r="X24" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y24" s="19" t="s">
+      <c r="Y24" s="38" t="s">
+        <v>637</v>
+      </c>
+      <c r="Z24" s="5"/>
+    </row>
+    <row r="25" spans="1:26" ht="60">
+      <c r="A25" s="21" t="s">
         <v>115</v>
-      </c>
-      <c r="Z24" s="5"/>
-    </row>
-    <row r="25" spans="1:26" ht="60" hidden="1">
-      <c r="A25" s="21" t="s">
-        <v>116</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="41" t="s">
         <v>119</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" s="41" t="s">
-        <v>120</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
@@ -17526,10 +17553,10 @@
         <v>58</v>
       </c>
       <c r="V25" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W25" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X25" s="5" t="s">
         <v>48</v>
@@ -17537,13 +17564,13 @@
       <c r="Y25" s="19"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" ht="45" hidden="1">
+    <row r="26" spans="1:26" ht="45">
       <c r="A26" s="21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>47</v>
@@ -17558,7 +17585,7 @@
         <v>48</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
@@ -17598,7 +17625,7 @@
         <v>58</v>
       </c>
       <c r="V26" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="W26" s="5" t="s">
         <v>47</v>
@@ -17609,13 +17636,13 @@
       <c r="Y26" s="19"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" ht="60" hidden="1">
+    <row r="27" spans="1:26" ht="60">
       <c r="A27" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>47</v>
@@ -17630,7 +17657,7 @@
         <v>48</v>
       </c>
       <c r="H27" s="41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -17670,7 +17697,7 @@
         <v>58</v>
       </c>
       <c r="V27" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="W27" s="5" t="s">
         <v>47</v>
@@ -17681,13 +17708,13 @@
       <c r="Y27" s="19"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" ht="109.5" hidden="1" customHeight="1">
+    <row r="28" spans="1:26" ht="109.5" customHeight="1">
       <c r="A28" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>71</v>
@@ -17702,7 +17729,7 @@
         <v>48</v>
       </c>
       <c r="H28" s="27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -17745,7 +17772,7 @@
         <v>58</v>
       </c>
       <c r="V28" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="W28" s="5" t="s">
         <v>71</v>
@@ -17756,13 +17783,13 @@
       <c r="Y28" s="19"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="90" hidden="1">
+    <row r="29" spans="1:26" ht="90">
       <c r="A29" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>111</v>
@@ -17777,7 +17804,7 @@
         <v>48</v>
       </c>
       <c r="H29" s="43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
@@ -17817,7 +17844,7 @@
         <v>58</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="W29" s="5" t="s">
         <v>111</v>
@@ -17828,13 +17855,13 @@
       <c r="Y29" s="19"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" ht="120" hidden="1">
+    <row r="30" spans="1:26" ht="120">
       <c r="A30" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>111</v>
@@ -17849,7 +17876,7 @@
         <v>48</v>
       </c>
       <c r="H30" s="41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -17890,7 +17917,7 @@
         <v>58</v>
       </c>
       <c r="V30" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="W30" s="5" t="s">
         <v>111</v>
@@ -17901,13 +17928,13 @@
       <c r="Y30" s="19"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" spans="1:26" ht="65.25" hidden="1" customHeight="1">
+    <row r="31" spans="1:26" ht="65.25" customHeight="1">
       <c r="A31" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>111</v>
@@ -17922,7 +17949,7 @@
         <v>48</v>
       </c>
       <c r="H31" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
@@ -17969,7 +17996,7 @@
         <v>58</v>
       </c>
       <c r="V31" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W31" s="5" t="s">
         <v>111</v>
@@ -17977,18 +18004,18 @@
       <c r="X31" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y31" s="19" t="s">
-        <v>146</v>
+      <c r="Y31" s="38" t="s">
+        <v>638</v>
       </c>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" ht="105" hidden="1">
+    <row r="32" spans="1:26" ht="105">
       <c r="A32" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>91</v>
@@ -18003,7 +18030,7 @@
         <v>48</v>
       </c>
       <c r="H32" s="41" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
@@ -18045,7 +18072,7 @@
         <v>58</v>
       </c>
       <c r="V32" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="W32" s="5" t="s">
         <v>91</v>
@@ -18056,13 +18083,13 @@
       <c r="Y32" s="19"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="1:26" ht="88.5" hidden="1" customHeight="1">
+    <row r="33" spans="1:26" ht="88.5" customHeight="1">
       <c r="A33" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>91</v>
@@ -18077,7 +18104,7 @@
         <v>48</v>
       </c>
       <c r="H33" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -18120,7 +18147,7 @@
         <v>58</v>
       </c>
       <c r="V33" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="W33" s="5" t="s">
         <v>91</v>
@@ -18131,13 +18158,13 @@
       <c r="Y33" s="19"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34" spans="1:26" ht="115.5" hidden="1" customHeight="1">
+    <row r="34" spans="1:26" ht="115.5" customHeight="1">
       <c r="A34" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>71</v>
@@ -18152,7 +18179,7 @@
         <v>48</v>
       </c>
       <c r="H34" s="27" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
@@ -18196,7 +18223,7 @@
         <v>58</v>
       </c>
       <c r="V34" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W34" s="5" t="s">
         <v>71</v>
@@ -18209,11 +18236,11 @@
     </row>
     <row r="35" spans="1:26" ht="89.25" customHeight="1">
       <c r="A35" s="21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>71</v>
@@ -18228,7 +18255,7 @@
         <v>48</v>
       </c>
       <c r="H35" s="42" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -18268,7 +18295,7 @@
       <c r="T35" s="3"/>
       <c r="U35" s="5"/>
       <c r="V35" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="W35" s="5" t="s">
         <v>71</v>
@@ -18279,13 +18306,13 @@
       <c r="Y35" s="19"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" spans="1:26" ht="75" hidden="1">
+    <row r="36" spans="1:26" ht="75">
       <c r="A36" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>111</v>
@@ -18300,7 +18327,7 @@
         <v>48</v>
       </c>
       <c r="H36" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
@@ -18338,7 +18365,7 @@
       <c r="T36" s="3"/>
       <c r="U36" s="5"/>
       <c r="V36" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="W36" s="5" t="s">
         <v>111</v>
@@ -18349,13 +18376,13 @@
       <c r="Y36" s="19"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" spans="1:26" ht="75" hidden="1">
+    <row r="37" spans="1:26" ht="75">
       <c r="A37" s="21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>71</v>
@@ -18370,7 +18397,7 @@
         <v>48</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -18411,7 +18438,7 @@
         <v>58</v>
       </c>
       <c r="V37" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W37" s="5" t="s">
         <v>71</v>
@@ -18420,17 +18447,17 @@
         <v>48</v>
       </c>
       <c r="Y37" s="46" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Z37" s="47"/>
     </row>
-    <row r="38" spans="1:26" ht="180" hidden="1">
+    <row r="38" spans="1:26" ht="180">
       <c r="A38" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>71</v>
@@ -18445,7 +18472,7 @@
         <v>48</v>
       </c>
       <c r="H38" s="41" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
@@ -18489,7 +18516,7 @@
         <v>58</v>
       </c>
       <c r="V38" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W38" s="5" t="s">
         <v>71</v>
@@ -18500,13 +18527,13 @@
       <c r="Y38" s="19"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39" spans="1:26" ht="84" hidden="1" customHeight="1">
+    <row r="39" spans="1:26" ht="84" customHeight="1">
       <c r="A39" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>111</v>
@@ -18521,7 +18548,7 @@
         <v>48</v>
       </c>
       <c r="H39" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
@@ -18563,7 +18590,7 @@
         <v>58</v>
       </c>
       <c r="V39" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="W39" s="5" t="s">
         <v>111</v>
@@ -18571,18 +18598,18 @@
       <c r="X39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y39" s="19" t="s">
-        <v>177</v>
+      <c r="Y39" s="38" t="s">
+        <v>639</v>
       </c>
       <c r="Z39" s="5"/>
     </row>
     <row r="40" spans="1:26" ht="126.75" customHeight="1">
       <c r="A40" s="21" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>47</v>
@@ -18597,7 +18624,7 @@
         <v>48</v>
       </c>
       <c r="H40" s="27" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
@@ -18639,10 +18666,10 @@
         <v>63</v>
       </c>
       <c r="U40" s="45" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="V40" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="W40" s="5" t="s">
         <v>47</v>
@@ -18651,17 +18678,17 @@
         <v>48</v>
       </c>
       <c r="Y40" s="40" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41" spans="1:26" ht="186.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:26" ht="186.75" customHeight="1">
       <c r="A41" s="21" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>111</v>
@@ -18676,7 +18703,7 @@
         <v>48</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -18720,7 +18747,7 @@
         <v>58</v>
       </c>
       <c r="V41" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="W41" s="5" t="s">
         <v>111</v>
@@ -18728,33 +18755,33 @@
       <c r="X41" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y41" s="19" t="s">
-        <v>188</v>
+      <c r="Y41" s="38" t="s">
+        <v>640</v>
       </c>
       <c r="Z41" s="5"/>
     </row>
     <row r="42" spans="1:26" ht="138" customHeight="1">
       <c r="A42" s="21" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H42" s="27" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -18797,23 +18824,23 @@
       </c>
       <c r="V42" s="5"/>
       <c r="W42" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="X42" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y42" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z42" s="5"/>
+    </row>
+    <row r="43" spans="1:26" ht="112.5" customHeight="1">
+      <c r="A43" s="21" t="s">
         <v>191</v>
-      </c>
-      <c r="X42" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y42" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z42" s="5"/>
-    </row>
-    <row r="43" spans="1:26" ht="112.5" hidden="1" customHeight="1">
-      <c r="A43" s="21" t="s">
-        <v>195</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>111</v>
@@ -18828,7 +18855,7 @@
         <v>48</v>
       </c>
       <c r="H43" s="41" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
@@ -18871,7 +18898,7 @@
         <v>58</v>
       </c>
       <c r="V43" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="W43" s="5" t="s">
         <v>111</v>
@@ -18879,18 +18906,18 @@
       <c r="X43" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y43" s="19" t="s">
-        <v>199</v>
+      <c r="Y43" s="38" t="s">
+        <v>641</v>
       </c>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44" spans="1:26" ht="84.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:26" ht="84.75" customHeight="1">
       <c r="A44" s="21" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>111</v>
@@ -18905,7 +18932,7 @@
         <v>48</v>
       </c>
       <c r="H44" s="27" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
@@ -18947,7 +18974,7 @@
         <v>58</v>
       </c>
       <c r="V44" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="W44" s="5" t="s">
         <v>111</v>
@@ -18955,33 +18982,33 @@
       <c r="X44" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y44" s="19" t="s">
-        <v>204</v>
+      <c r="Y44" s="38" t="s">
+        <v>642</v>
       </c>
       <c r="Z44" s="5"/>
     </row>
     <row r="45" spans="1:26" ht="409.5">
       <c r="A45" s="21" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
@@ -19031,23 +19058,23 @@
       </c>
       <c r="V45" s="5"/>
       <c r="W45" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="X45" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Y45" s="19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" spans="1:26" ht="90" hidden="1">
+    <row r="46" spans="1:26" ht="90">
       <c r="A46" s="21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="5" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>111</v>
@@ -19062,7 +19089,7 @@
         <v>48</v>
       </c>
       <c r="H46" s="42" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -19099,7 +19126,7 @@
       <c r="T46" s="3"/>
       <c r="U46" s="5"/>
       <c r="V46" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="W46" s="5" t="s">
         <v>111</v>
@@ -19110,13 +19137,13 @@
       <c r="Y46" s="19"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" spans="1:26" ht="136.5" hidden="1" customHeight="1">
+    <row r="47" spans="1:26" ht="136.5" customHeight="1">
       <c r="A47" s="21" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="5" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>111</v>
@@ -19131,7 +19158,7 @@
         <v>48</v>
       </c>
       <c r="H47" s="27" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
@@ -19175,7 +19202,7 @@
         <v>58</v>
       </c>
       <c r="V47" s="5" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="W47" s="5" t="s">
         <v>111</v>
@@ -19188,11 +19215,11 @@
     </row>
     <row r="48" spans="1:26" ht="271.5" customHeight="1">
       <c r="A48" s="21" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B48" s="21"/>
       <c r="C48" s="5" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>47</v>
@@ -19207,7 +19234,7 @@
         <v>48</v>
       </c>
       <c r="H48" s="27" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
@@ -19255,10 +19282,10 @@
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="V48" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="W48" s="5" t="s">
         <v>47</v>
@@ -19267,17 +19294,17 @@
         <v>48</v>
       </c>
       <c r="Y48" s="19" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49" spans="1:26" ht="112.5" hidden="1" customHeight="1">
+    <row r="49" spans="1:26" ht="112.5" customHeight="1">
       <c r="A49" s="21" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B49" s="21"/>
       <c r="C49" s="5" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>71</v>
@@ -19292,7 +19319,7 @@
         <v>48</v>
       </c>
       <c r="H49" s="27" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
@@ -19336,7 +19363,7 @@
         <v>58</v>
       </c>
       <c r="V49" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="W49" s="5" t="s">
         <v>71</v>
@@ -19347,13 +19374,13 @@
       <c r="Y49" s="19"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50" spans="1:26" ht="90" hidden="1">
+    <row r="50" spans="1:26" ht="90">
       <c r="A50" s="21" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="5" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>91</v>
@@ -19368,7 +19395,7 @@
         <v>48</v>
       </c>
       <c r="H50" s="27" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
@@ -19409,7 +19436,7 @@
         <v>58</v>
       </c>
       <c r="V50" s="5" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="W50" s="5" t="s">
         <v>91</v>
@@ -19420,28 +19447,28 @@
       <c r="Y50" s="19"/>
       <c r="Z50" s="5"/>
     </row>
-    <row r="51" spans="1:26" ht="30" hidden="1">
+    <row r="51" spans="1:26" ht="30">
       <c r="A51" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H51" s="41" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -19480,10 +19507,10 @@
         <v>58</v>
       </c>
       <c r="V51" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="W51" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="X51" s="5" t="s">
         <v>48</v>
@@ -19491,13 +19518,13 @@
       <c r="Y51" s="19"/>
       <c r="Z51" s="5"/>
     </row>
-    <row r="52" spans="1:26" ht="60" hidden="1">
+    <row r="52" spans="1:26" ht="60">
       <c r="A52" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>91</v>
@@ -19512,7 +19539,7 @@
         <v>48</v>
       </c>
       <c r="H52" s="41" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -19553,7 +19580,7 @@
         <v>58</v>
       </c>
       <c r="V52" s="5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="W52" s="5" t="s">
         <v>91</v>
@@ -19566,11 +19593,11 @@
     </row>
     <row r="53" spans="1:26" ht="60">
       <c r="A53" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="5" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>47</v>
@@ -19585,7 +19612,7 @@
         <v>48</v>
       </c>
       <c r="H53" s="42" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
@@ -19632,17 +19659,17 @@
         <v>48</v>
       </c>
       <c r="Y53" s="19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="Z53" s="5"/>
     </row>
-    <row r="54" spans="1:26" ht="45" hidden="1">
+    <row r="54" spans="1:26" ht="45">
       <c r="A54" s="21" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>111</v>
@@ -19657,7 +19684,7 @@
         <v>48</v>
       </c>
       <c r="H54" s="41" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
@@ -19697,7 +19724,7 @@
         <v>58</v>
       </c>
       <c r="V54" s="5" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="W54" s="5" t="s">
         <v>111</v>
@@ -19705,18 +19732,18 @@
       <c r="X54" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y54" s="19" t="s">
-        <v>243</v>
+      <c r="Y54" s="38" t="s">
+        <v>643</v>
       </c>
       <c r="Z54" s="5"/>
     </row>
-    <row r="55" spans="1:26" ht="45" hidden="1">
+    <row r="55" spans="1:26" ht="45">
       <c r="A55" s="21" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>111</v>
@@ -19731,7 +19758,7 @@
         <v>48</v>
       </c>
       <c r="H55" s="27" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
@@ -19771,7 +19798,7 @@
         <v>58</v>
       </c>
       <c r="V55" s="5" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="W55" s="5" t="s">
         <v>111</v>
@@ -19779,18 +19806,18 @@
       <c r="X55" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y55" s="19" t="s">
-        <v>243</v>
+      <c r="Y55" s="38" t="s">
+        <v>643</v>
       </c>
       <c r="Z55" s="5"/>
     </row>
-    <row r="56" spans="1:26" ht="60" hidden="1">
+    <row r="56" spans="1:26" ht="60">
       <c r="A56" s="21" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B56" s="21"/>
       <c r="C56" s="5" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>71</v>
@@ -19805,7 +19832,7 @@
         <v>48</v>
       </c>
       <c r="H56" s="42" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
@@ -19845,7 +19872,7 @@
         <v>58</v>
       </c>
       <c r="V56" s="5" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="W56" s="5" t="s">
         <v>71</v>
@@ -19856,28 +19883,28 @@
       <c r="Y56" s="19"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57" spans="1:26" ht="60" hidden="1">
+    <row r="57" spans="1:26" ht="60">
       <c r="A57" s="21" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="5" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H57" s="41" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -19917,10 +19944,10 @@
         <v>58</v>
       </c>
       <c r="V57" s="5" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="W57" s="5" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="X57" s="5" t="s">
         <v>48</v>
@@ -19928,13 +19955,13 @@
       <c r="Y57" s="19"/>
       <c r="Z57" s="5"/>
     </row>
-    <row r="58" spans="1:26" ht="345" hidden="1">
+    <row r="58" spans="1:26" ht="345">
       <c r="A58" s="21" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="5" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>101</v>
@@ -19949,7 +19976,7 @@
         <v>48</v>
       </c>
       <c r="H58" s="27" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -19984,22 +20011,22 @@
       <c r="T58" s="3"/>
       <c r="U58" s="5"/>
       <c r="V58" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="W58" s="5"/>
       <c r="X58" s="5"/>
       <c r="Y58" s="38" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="Z58" s="5"/>
     </row>
-    <row r="59" spans="1:26" ht="60" hidden="1">
+    <row r="59" spans="1:26" ht="60">
       <c r="A59" s="21" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="5" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>111</v>
@@ -20014,7 +20041,7 @@
         <v>48</v>
       </c>
       <c r="H59" s="41" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -20054,7 +20081,7 @@
         <v>58</v>
       </c>
       <c r="V59" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="W59" s="5" t="s">
         <v>111</v>
@@ -20065,13 +20092,13 @@
       <c r="Y59" s="38"/>
       <c r="Z59" s="5"/>
     </row>
-    <row r="60" spans="1:26" ht="105" hidden="1">
+    <row r="60" spans="1:26" ht="105">
       <c r="A60" s="21" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="5" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>111</v>
@@ -20086,7 +20113,7 @@
         <v>48</v>
       </c>
       <c r="H60" s="41" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
@@ -20135,18 +20162,18 @@
       <c r="X60" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y60" s="19" t="s">
-        <v>115</v>
+      <c r="Y60" s="38" t="s">
+        <v>637</v>
       </c>
       <c r="Z60" s="5"/>
     </row>
-    <row r="61" spans="1:26" ht="122.25" hidden="1" customHeight="1">
+    <row r="61" spans="1:26" ht="122.25" customHeight="1">
       <c r="A61" s="21" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="5" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>111</v>
@@ -20161,7 +20188,7 @@
         <v>48</v>
       </c>
       <c r="H61" s="41" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -20207,7 +20234,7 @@
         <v>58</v>
       </c>
       <c r="V61" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W61" s="5" t="s">
         <v>111</v>
@@ -20215,18 +20242,18 @@
       <c r="X61" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y61" s="19" t="s">
-        <v>146</v>
+      <c r="Y61" s="38" t="s">
+        <v>638</v>
       </c>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62" spans="1:26" ht="99.75" hidden="1" customHeight="1">
+    <row r="62" spans="1:26" ht="99.75" customHeight="1">
       <c r="A62" s="21" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B62" s="21"/>
       <c r="C62" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>111</v>
@@ -20241,7 +20268,7 @@
         <v>48</v>
       </c>
       <c r="H62" s="27" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -20283,7 +20310,7 @@
         <v>58</v>
       </c>
       <c r="V62" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="W62" s="5" t="s">
         <v>111</v>
@@ -20291,18 +20318,18 @@
       <c r="X62" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y62" s="19" t="s">
-        <v>177</v>
+      <c r="Y62" s="38" t="s">
+        <v>639</v>
       </c>
       <c r="Z62" s="5"/>
     </row>
-    <row r="63" spans="1:26" ht="158.25" hidden="1" customHeight="1">
+    <row r="63" spans="1:26" ht="158.25" customHeight="1">
       <c r="A63" s="21" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="5" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>111</v>
@@ -20317,7 +20344,7 @@
         <v>48</v>
       </c>
       <c r="H63" s="27" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -20361,7 +20388,7 @@
         <v>58</v>
       </c>
       <c r="V63" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="W63" s="5" t="s">
         <v>111</v>
@@ -20369,33 +20396,33 @@
       <c r="X63" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y63" s="19" t="s">
-        <v>188</v>
+      <c r="Y63" s="38" t="s">
+        <v>640</v>
       </c>
       <c r="Z63" s="5"/>
     </row>
-    <row r="64" spans="1:26" ht="210" hidden="1">
+    <row r="64" spans="1:26" ht="210">
       <c r="A64" s="21" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B64" s="21"/>
       <c r="C64" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H64" s="27" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
@@ -20438,26 +20465,26 @@
         <v>58</v>
       </c>
       <c r="V64" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="W64" s="5" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="X64" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y64" s="19" t="s">
-        <v>199</v>
+      <c r="Y64" s="38" t="s">
+        <v>641</v>
       </c>
       <c r="Z64" s="5"/>
     </row>
-    <row r="65" spans="1:26" ht="135" hidden="1">
+    <row r="65" spans="1:26" ht="135">
       <c r="A65" s="21" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B65" s="21"/>
       <c r="C65" s="5" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>111</v>
@@ -20472,7 +20499,7 @@
         <v>48</v>
       </c>
       <c r="H65" s="27" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -20514,7 +20541,7 @@
         <v>58</v>
       </c>
       <c r="V65" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="W65" s="5" t="s">
         <v>111</v>
@@ -20522,18 +20549,18 @@
       <c r="X65" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y65" s="19" t="s">
-        <v>204</v>
+      <c r="Y65" s="38" t="s">
+        <v>642</v>
       </c>
       <c r="Z65" s="5"/>
     </row>
-    <row r="66" spans="1:26" ht="45" hidden="1">
+    <row r="66" spans="1:26" ht="45">
       <c r="A66" s="21" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B66" s="21"/>
       <c r="C66" s="5" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>41</v>
@@ -20548,7 +20575,7 @@
         <v>48</v>
       </c>
       <c r="H66" s="27" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
@@ -20588,7 +20615,7 @@
         <v>58</v>
       </c>
       <c r="V66" s="5" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="W66" s="5" t="s">
         <v>41</v>
@@ -20599,28 +20626,28 @@
       <c r="Y66" s="19"/>
       <c r="Z66" s="5"/>
     </row>
-    <row r="67" spans="1:26" ht="90" hidden="1">
+    <row r="67" spans="1:26" ht="90">
       <c r="A67" s="21" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B67" s="21"/>
       <c r="C67" s="5" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H67" s="27" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
@@ -20661,26 +20688,26 @@
         <v>52</v>
       </c>
       <c r="V67" s="5" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="W67" s="5" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="X67" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Y67" s="19" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="Z67" s="5"/>
     </row>
-    <row r="68" spans="1:26" ht="90" hidden="1">
+    <row r="68" spans="1:26" ht="90">
       <c r="A68" s="21" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B68" s="21"/>
       <c r="C68" s="5" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>41</v>
@@ -20695,7 +20722,7 @@
         <v>48</v>
       </c>
       <c r="H68" s="27" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
@@ -20735,7 +20762,7 @@
         <v>104</v>
       </c>
       <c r="V68" s="5" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="W68" s="5" t="s">
         <v>41</v>
@@ -20744,17 +20771,17 @@
         <v>48</v>
       </c>
       <c r="Y68" s="38" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="Z68" s="5"/>
     </row>
-    <row r="69" spans="1:26" ht="409.5" hidden="1">
+    <row r="69" spans="1:26" ht="409.5">
       <c r="A69" s="21" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B69" s="21"/>
       <c r="C69" s="5" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>101</v>
@@ -20769,7 +20796,7 @@
         <v>48</v>
       </c>
       <c r="H69" s="27" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
@@ -20824,27 +20851,27 @@
         <v>63</v>
       </c>
       <c r="U69" s="45" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="V69" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="W69" s="5"/>
       <c r="X69" s="5" t="s">
         <v>48</v>
       </c>
       <c r="Y69" s="19" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="Z69" s="5"/>
     </row>
-    <row r="70" spans="1:26" ht="105" hidden="1">
+    <row r="70" spans="1:26" ht="105">
       <c r="A70" s="21" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B70" s="21"/>
       <c r="C70" s="5" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>71</v>
@@ -20859,7 +20886,7 @@
         <v>48</v>
       </c>
       <c r="H70" s="27" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
@@ -20900,7 +20927,7 @@
         <v>58</v>
       </c>
       <c r="V70" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="W70" s="5" t="s">
         <v>71</v>
@@ -20909,17 +20936,17 @@
         <v>48</v>
       </c>
       <c r="Y70" s="19" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="Z70" s="5"/>
     </row>
-    <row r="71" spans="1:26" s="39" customFormat="1" ht="240" hidden="1">
+    <row r="71" spans="1:26" s="39" customFormat="1" ht="240">
       <c r="A71" s="21" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="21" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D71" s="21" t="s">
         <v>71</v>
@@ -20934,7 +20961,7 @@
         <v>48</v>
       </c>
       <c r="H71" s="29" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="I71" s="21"/>
       <c r="J71" s="21"/>
@@ -20987,17 +21014,17 @@
         <v>48</v>
       </c>
       <c r="Y71" s="46" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="Z71" s="47"/>
     </row>
-    <row r="72" spans="1:26" hidden="1">
+    <row r="72" spans="1:26">
       <c r="A72" s="21" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>41</v>
@@ -21012,7 +21039,7 @@
         <v>48</v>
       </c>
       <c r="H72" s="27" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -21053,28 +21080,28 @@
       <c r="Y72" s="19"/>
       <c r="Z72" s="5"/>
     </row>
-    <row r="73" spans="1:26" hidden="1">
+    <row r="73" spans="1:26">
       <c r="A73" s="21" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B73" s="21"/>
       <c r="C73" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H73" s="27" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
@@ -21115,28 +21142,28 @@
       <c r="Y73" s="19"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74" spans="1:26" ht="30" hidden="1">
+    <row r="74" spans="1:26" ht="30">
       <c r="A74" s="21" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B74" s="21"/>
       <c r="C74" s="5" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H74" s="27" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
@@ -21177,28 +21204,28 @@
       <c r="Y74" s="19"/>
       <c r="Z74" s="5"/>
     </row>
-    <row r="75" spans="1:26" ht="30" hidden="1">
+    <row r="75" spans="1:26" ht="30">
       <c r="A75" s="21" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B75" s="21"/>
       <c r="C75" s="5" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H75" s="27" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
@@ -21239,28 +21266,28 @@
       <c r="Y75" s="19"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76" spans="1:26" ht="30" hidden="1">
+    <row r="76" spans="1:26" ht="30">
       <c r="A76" s="21" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B76" s="21"/>
       <c r="C76" s="5" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H76" s="27" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
@@ -21494,18 +21521,7 @@
       <c r="A140" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:AA76" xr:uid="{9B3FCE14-916F-44E5-ADDA-A49F8526702E}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="LOSS_NOT_ALWD_F"/>
-        <filter val="OPN_TXN_EV_TP"/>
-        <filter val="ORIG_EV_TP"/>
-        <filter val="ORIG_TXN_TP_CD"/>
-        <filter val="SRC_RCRD_TP_CD"/>
-        <filter val="TXN_TP_CD"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A9:AA76" xr:uid="{9B3FCE14-916F-44E5-ADDA-A49F8526702E}"/>
   <mergeCells count="7">
     <mergeCell ref="Y71:Z71"/>
     <mergeCell ref="Y37:Z37"/>
@@ -21541,36 +21557,36 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H1" t="s">
         <v>324</v>
       </c>
-      <c r="B1" t="s">
+      <c r="I1" t="s">
         <v>325</v>
-      </c>
-      <c r="C1" t="s">
-        <v>326</v>
-      </c>
-      <c r="D1" t="s">
-        <v>327</v>
-      </c>
-      <c r="E1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F1" t="s">
-        <v>329</v>
-      </c>
-      <c r="G1" t="s">
-        <v>330</v>
-      </c>
-      <c r="H1" t="s">
-        <v>331</v>
-      </c>
-      <c r="I1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B2" t="s">
         <v>101</v>
@@ -21582,18 +21598,18 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -21605,18 +21621,18 @@
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H3" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I3" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
@@ -21628,21 +21644,21 @@
         <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
@@ -21651,21 +21667,21 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H5" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I5" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B6" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C6" t="s">
         <v>48</v>
@@ -21674,18 +21690,18 @@
         <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H6" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I6" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
         <v>101</v>
@@ -21697,18 +21713,18 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H7" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I7" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
@@ -21720,21 +21736,21 @@
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H8" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I8" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B9" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -21743,18 +21759,18 @@
         <v>72</v>
       </c>
       <c r="G9" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H9" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I9" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
         <v>111</v>
@@ -21766,18 +21782,18 @@
         <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H10" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I10" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
@@ -21789,18 +21805,18 @@
         <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B12" t="s">
         <v>59</v>
@@ -21812,21 +21828,21 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H12" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I12" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B13" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C13" t="s">
         <v>48</v>
@@ -21835,18 +21851,18 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H13" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I13" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B14" t="s">
         <v>59</v>
@@ -21858,18 +21874,18 @@
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H14" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I14" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -21881,18 +21897,18 @@
         <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H15" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I15" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
@@ -21904,18 +21920,18 @@
         <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H16" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I16" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B17" t="s">
         <v>59</v>
@@ -21927,18 +21943,18 @@
         <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H17" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I17" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B18" t="s">
         <v>111</v>
@@ -21950,18 +21966,18 @@
         <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H18" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I18" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
@@ -21973,18 +21989,18 @@
         <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H19" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I19" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
@@ -21996,18 +22012,18 @@
         <v>79</v>
       </c>
       <c r="G20" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H20" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I20" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B21" t="s">
         <v>71</v>
@@ -22019,21 +22035,21 @@
         <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H21" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I21" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B22" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C22" t="s">
         <v>42</v>
@@ -22042,21 +22058,21 @@
         <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H22" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I22" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C23" t="s">
         <v>42</v>
@@ -22065,21 +22081,21 @@
         <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H23" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I23" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
         <v>48</v>
@@ -22088,18 +22104,18 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H24" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I24" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B25" t="s">
         <v>111</v>
@@ -22111,18 +22127,18 @@
         <v>25</v>
       </c>
       <c r="G25" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H25" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I25" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B26" t="s">
         <v>71</v>
@@ -22134,18 +22150,18 @@
         <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H26" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I26" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B27" t="s">
         <v>91</v>
@@ -22157,21 +22173,21 @@
         <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H27" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I27" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B28" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C28" t="s">
         <v>42</v>
@@ -22180,18 +22196,18 @@
         <v>70</v>
       </c>
       <c r="G28" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H28" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I28" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B29" t="s">
         <v>91</v>
@@ -22203,21 +22219,21 @@
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H29" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I29" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B30" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C30" t="s">
         <v>42</v>
@@ -22226,18 +22242,18 @@
         <v>71</v>
       </c>
       <c r="G30" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H30" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I30" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B31" t="s">
         <v>111</v>
@@ -22249,18 +22265,18 @@
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H31" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I31" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B32" t="s">
         <v>111</v>
@@ -22272,18 +22288,18 @@
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H32" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I32" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B33" t="s">
         <v>91</v>
@@ -22295,21 +22311,21 @@
         <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H33" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I33" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C34" t="s">
         <v>42</v>
@@ -22318,21 +22334,21 @@
         <v>73</v>
       </c>
       <c r="G34" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H34" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I34" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B35" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C35" t="s">
         <v>42</v>
@@ -22341,21 +22357,21 @@
         <v>68</v>
       </c>
       <c r="G35" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H35" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I35" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B36" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C36" t="s">
         <v>42</v>
@@ -22364,18 +22380,18 @@
         <v>69</v>
       </c>
       <c r="G36" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H36" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I36" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B37" t="s">
         <v>111</v>
@@ -22387,18 +22403,18 @@
         <v>32</v>
       </c>
       <c r="G37" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H37" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I37" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B38" t="s">
         <v>71</v>
@@ -22410,18 +22426,18 @@
         <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H38" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I38" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s">
         <v>71</v>
@@ -22433,18 +22449,18 @@
         <v>31</v>
       </c>
       <c r="G39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s">
         <v>71</v>
@@ -22456,18 +22472,18 @@
         <v>33</v>
       </c>
       <c r="G40" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H40" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I40" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s">
         <v>71</v>
@@ -22479,18 +22495,18 @@
         <v>81</v>
       </c>
       <c r="G41" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H41" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I41" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s">
         <v>111</v>
@@ -22502,21 +22518,21 @@
         <v>35</v>
       </c>
       <c r="G42" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H42" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I42" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="B43" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C43" t="s">
         <v>42</v>
@@ -22525,18 +22541,18 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H43" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I43" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B44" t="s">
         <v>47</v>
@@ -22548,21 +22564,21 @@
         <v>36</v>
       </c>
       <c r="G44" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H44" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I44" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C45" t="s">
         <v>48</v>
@@ -22571,18 +22587,18 @@
         <v>38</v>
       </c>
       <c r="G45" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H45" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I45" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B46" t="s">
         <v>111</v>
@@ -22594,18 +22610,18 @@
         <v>39</v>
       </c>
       <c r="G46" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H46" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I46" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s">
         <v>111</v>
@@ -22617,21 +22633,21 @@
         <v>40</v>
       </c>
       <c r="G47" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H47" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I47" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C48" t="s">
         <v>48</v>
@@ -22640,18 +22656,18 @@
         <v>41</v>
       </c>
       <c r="G48" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H48" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I48" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B49" t="s">
         <v>91</v>
@@ -22663,21 +22679,21 @@
         <v>29</v>
       </c>
       <c r="G49" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H49" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I49" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C50" t="s">
         <v>42</v>
@@ -22686,18 +22702,18 @@
         <v>76</v>
       </c>
       <c r="G50" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H50" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I50" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B51" t="s">
         <v>111</v>
@@ -22709,18 +22725,18 @@
         <v>42</v>
       </c>
       <c r="G51" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H51" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I51" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s">
         <v>111</v>
@@ -22732,18 +22748,18 @@
         <v>43</v>
       </c>
       <c r="G52" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H52" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I52" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s">
         <v>71</v>
@@ -22755,18 +22771,18 @@
         <v>45</v>
       </c>
       <c r="G53" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H53" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I53" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s">
         <v>91</v>
@@ -22778,21 +22794,21 @@
         <v>46</v>
       </c>
       <c r="G54" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H54" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I54" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C55" t="s">
         <v>42</v>
@@ -22801,18 +22817,18 @@
         <v>74</v>
       </c>
       <c r="G55" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H55" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I55" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B56" t="s">
         <v>91</v>
@@ -22824,18 +22840,18 @@
         <v>47</v>
       </c>
       <c r="G56" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H56" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I56" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B57" t="s">
         <v>47</v>
@@ -22847,18 +22863,18 @@
         <v>44</v>
       </c>
       <c r="G57" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H57" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I57" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B58" t="s">
         <v>47</v>
@@ -22870,21 +22886,21 @@
         <v>2</v>
       </c>
       <c r="G58" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H58" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I58" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B59" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C59" t="s">
         <v>42</v>
@@ -22893,21 +22909,21 @@
         <v>77</v>
       </c>
       <c r="G59" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H59" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I59" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B60" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C60" t="s">
         <v>48</v>
@@ -22916,21 +22932,21 @@
         <v>65</v>
       </c>
       <c r="G60" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H60" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I60" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B61" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C61" t="s">
         <v>48</v>
@@ -22939,18 +22955,18 @@
         <v>66</v>
       </c>
       <c r="G61" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H61" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I61" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B62" t="s">
         <v>111</v>
@@ -22962,18 +22978,18 @@
         <v>57</v>
       </c>
       <c r="G62" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H62" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I62" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B63" t="s">
         <v>111</v>
@@ -22985,18 +23001,18 @@
         <v>60</v>
       </c>
       <c r="G63" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H63" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I63" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B64" t="s">
         <v>111</v>
@@ -23008,18 +23024,18 @@
         <v>56</v>
       </c>
       <c r="G64" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H64" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I64" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B65" t="s">
         <v>111</v>
@@ -23031,18 +23047,18 @@
         <v>58</v>
       </c>
       <c r="G65" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H65" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I65" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B66" t="s">
         <v>111</v>
@@ -23054,21 +23070,21 @@
         <v>59</v>
       </c>
       <c r="G66" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H66" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I66" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B67" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C67" t="s">
         <v>48</v>
@@ -23077,18 +23093,18 @@
         <v>61</v>
       </c>
       <c r="G67" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H67" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I67" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B68" t="s">
         <v>111</v>
@@ -23100,18 +23116,18 @@
         <v>62</v>
       </c>
       <c r="G68" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H68" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I68" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B69" t="s">
         <v>111</v>
@@ -23123,18 +23139,18 @@
         <v>52</v>
       </c>
       <c r="G69" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H69" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I69" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B70" t="s">
         <v>77</v>
@@ -23146,21 +23162,21 @@
         <v>7</v>
       </c>
       <c r="G70" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H70" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I70" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B71" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C71" t="s">
         <v>48</v>
@@ -23169,18 +23185,18 @@
         <v>10</v>
       </c>
       <c r="G71" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H71" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I71" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B72" t="s">
         <v>47</v>
@@ -23192,21 +23208,21 @@
         <v>8</v>
       </c>
       <c r="G72" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H72" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I72" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B73" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C73" t="s">
         <v>48</v>
@@ -23215,18 +23231,18 @@
         <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H73" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I73" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B74" t="s">
         <v>101</v>
@@ -23238,21 +23254,21 @@
         <v>78</v>
       </c>
       <c r="G74" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H74" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I74" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B75" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
         <v>48</v>
@@ -23261,18 +23277,18 @@
         <v>48</v>
       </c>
       <c r="G75" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H75" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I75" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B76" t="s">
         <v>91</v>
@@ -23284,21 +23300,21 @@
         <v>49</v>
       </c>
       <c r="G76" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H76" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I76" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B77" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C77" t="s">
         <v>42</v>
@@ -23307,18 +23323,18 @@
         <v>75</v>
       </c>
       <c r="G77" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H77" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I77" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B78" t="s">
         <v>47</v>
@@ -23330,18 +23346,18 @@
         <v>50</v>
       </c>
       <c r="G78" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H78" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I78" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B79" t="s">
         <v>111</v>
@@ -23353,18 +23369,18 @@
         <v>51</v>
       </c>
       <c r="G79" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H79" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I79" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B80" t="s">
         <v>71</v>
@@ -23376,18 +23392,18 @@
         <v>53</v>
       </c>
       <c r="G80" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H80" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I80" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B81" t="s">
         <v>101</v>
@@ -23399,21 +23415,21 @@
         <v>55</v>
       </c>
       <c r="G81" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H81" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I81" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B82" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C82" t="s">
         <v>48</v>
@@ -23422,13 +23438,13 @@
         <v>54</v>
       </c>
       <c r="G82" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H82" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="I82" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -23468,7 +23484,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="15" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -23478,17 +23494,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="15" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="15" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="16" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -23509,54 +23525,54 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>414</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="H1" s="36" t="s">
         <v>420</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>421</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>422</v>
-      </c>
-      <c r="D1" s="36" t="s">
-        <v>423</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>424</v>
-      </c>
-      <c r="F1" s="36" t="s">
-        <v>425</v>
-      </c>
-      <c r="G1" s="36" t="s">
-        <v>426</v>
-      </c>
-      <c r="H1" s="36" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="153.75">
       <c r="A2" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>101</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I2" s="26"/>
       <c r="J2" s="26">
@@ -23565,28 +23581,28 @@
     </row>
     <row r="3" spans="1:10" ht="153.75">
       <c r="A3" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>427</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="E3" s="35" t="s">
         <v>429</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>434</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>436</v>
-      </c>
       <c r="F3" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I3" s="26"/>
       <c r="J3" s="26">
@@ -23595,10 +23611,10 @@
     </row>
     <row r="4" spans="1:10" ht="141">
       <c r="A4" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>69</v>
@@ -23607,16 +23623,16 @@
         <v>70</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I4" s="26"/>
       <c r="J4" s="26">
@@ -23625,28 +23641,28 @@
     </row>
     <row r="5" spans="1:10" ht="64.5">
       <c r="A5" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I5" s="26"/>
       <c r="J5" s="26">
@@ -23655,28 +23671,28 @@
     </row>
     <row r="6" spans="1:10" ht="64.5">
       <c r="A6" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I6" s="26"/>
       <c r="J6" s="26">
@@ -23685,10 +23701,10 @@
     </row>
     <row r="7" spans="1:10" ht="77.25">
       <c r="A7" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C7" s="26" t="s">
         <v>99</v>
@@ -23697,16 +23713,16 @@
         <v>100</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>101</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I7" s="26"/>
       <c r="J7" s="26">
@@ -23715,10 +23731,10 @@
     </row>
     <row r="8" spans="1:10" ht="64.5">
       <c r="A8" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>106</v>
@@ -23727,16 +23743,16 @@
         <v>107</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>91</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I8" s="26"/>
       <c r="J8" s="26">
@@ -23745,28 +23761,28 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I9" s="26"/>
       <c r="J9" s="26">
@@ -23775,10 +23791,10 @@
     </row>
     <row r="10" spans="1:10" ht="77.25">
       <c r="A10" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>109</v>
@@ -23787,16 +23803,16 @@
         <v>110</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I10" s="26"/>
       <c r="J10" s="26">
@@ -23805,28 +23821,28 @@
     </row>
     <row r="11" spans="1:10" ht="115.5">
       <c r="A11" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I11" s="26"/>
       <c r="J11" s="26">
@@ -23835,28 +23851,28 @@
     </row>
     <row r="12" spans="1:10" ht="64.5">
       <c r="A12" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I12" s="26"/>
       <c r="J12" s="26">
@@ -23865,10 +23881,10 @@
     </row>
     <row r="13" spans="1:10" ht="39">
       <c r="A13" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C13" s="26" t="s">
         <v>54</v>
@@ -23877,16 +23893,16 @@
         <v>55</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I13" s="26"/>
       <c r="J13" s="26">
@@ -23895,28 +23911,28 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="26">
@@ -23925,26 +23941,26 @@
     </row>
     <row r="15" spans="1:10" ht="64.5">
       <c r="A15" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="26" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I15" s="26"/>
       <c r="J15" s="26">
@@ -23953,10 +23969,10 @@
     </row>
     <row r="16" spans="1:10" ht="64.5">
       <c r="A16" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C16" s="26" t="s">
         <v>66</v>
@@ -23965,16 +23981,16 @@
         <v>67</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I16" s="26"/>
       <c r="J16" s="26">
@@ -23983,28 +23999,28 @@
     </row>
     <row r="17" spans="1:10" ht="39">
       <c r="A17" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>123</v>
-      </c>
       <c r="E17" s="35" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="26">
@@ -24013,28 +24029,28 @@
     </row>
     <row r="18" spans="1:10" ht="51.75">
       <c r="A18" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C18" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>127</v>
-      </c>
       <c r="E18" s="35" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I18" s="26"/>
       <c r="J18" s="26">
@@ -24043,10 +24059,10 @@
     </row>
     <row r="19" spans="1:10" ht="77.25">
       <c r="A19" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C19" s="26" t="s">
         <v>60</v>
@@ -24055,16 +24071,16 @@
         <v>61</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="H19" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I19" s="26"/>
       <c r="J19" s="26">
@@ -24073,28 +24089,28 @@
     </row>
     <row r="20" spans="1:10" ht="243">
       <c r="A20" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I20" s="26"/>
       <c r="J20" s="26">
@@ -24103,28 +24119,28 @@
     </row>
     <row r="21" spans="1:10" ht="153.75">
       <c r="A21" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C21" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>131</v>
-      </c>
       <c r="E21" s="35" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I21" s="26"/>
       <c r="J21" s="26">
@@ -24133,28 +24149,28 @@
     </row>
     <row r="22" spans="1:10" ht="90">
       <c r="A22" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I22" s="26"/>
       <c r="J22" s="26">
@@ -24163,28 +24179,28 @@
     </row>
     <row r="23" spans="1:10" ht="51.75">
       <c r="A23" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I23" s="26"/>
       <c r="J23" s="26">
@@ -24193,26 +24209,26 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E24" s="26"/>
       <c r="F24" s="26" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I24" s="26"/>
       <c r="J24" s="26">
@@ -24221,28 +24237,28 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I25" s="26"/>
       <c r="J25" s="26">
@@ -24251,26 +24267,26 @@
     </row>
     <row r="26" spans="1:10" ht="51.75">
       <c r="A26" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C26" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="26" t="s">
-        <v>117</v>
-      </c>
       <c r="E26" s="35" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F26" s="26"/>
       <c r="G26" s="26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I26" s="26"/>
       <c r="J26" s="26">
@@ -24279,28 +24295,28 @@
     </row>
     <row r="27" spans="1:10" ht="51.75">
       <c r="A27" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G27" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I27" s="26"/>
       <c r="J27" s="26">
@@ -24309,28 +24325,28 @@
     </row>
     <row r="28" spans="1:10" ht="281.25">
       <c r="A28" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G28" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I28" s="26"/>
       <c r="J28" s="26">
@@ -24339,19 +24355,19 @@
     </row>
     <row r="29" spans="1:10" ht="51.75">
       <c r="A29" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C29" s="26" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="F29" s="26" t="s">
         <v>95</v>
@@ -24360,7 +24376,7 @@
         <v>91</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I29" s="26"/>
       <c r="J29" s="26">
@@ -24369,28 +24385,28 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I30" s="26"/>
       <c r="J30" s="26">
@@ -24399,10 +24415,10 @@
     </row>
     <row r="31" spans="1:10" ht="39">
       <c r="A31" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>89</v>
@@ -24411,14 +24427,14 @@
         <v>90</v>
       </c>
       <c r="E31" s="35" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F31" s="26"/>
       <c r="G31" s="26" t="s">
         <v>91</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I31" s="26"/>
       <c r="J31" s="26">
@@ -24427,28 +24443,28 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I32" s="26"/>
       <c r="J32" s="26">
@@ -24457,28 +24473,28 @@
     </row>
     <row r="33" spans="1:10" ht="102.75">
       <c r="A33" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C33" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D33" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="26" t="s">
-        <v>139</v>
-      </c>
       <c r="E33" s="35" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G33" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I33" s="26"/>
       <c r="J33" s="26">
@@ -24487,28 +24503,28 @@
     </row>
     <row r="34" spans="1:10" ht="166.5">
       <c r="A34" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C34" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="D34" s="26" t="s">
-        <v>143</v>
-      </c>
       <c r="E34" s="35" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I34" s="26"/>
       <c r="J34" s="26">
@@ -24517,26 +24533,26 @@
     </row>
     <row r="35" spans="1:10" ht="90">
       <c r="A35" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F35" s="26"/>
       <c r="G35" s="26" t="s">
         <v>91</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I35" s="26"/>
       <c r="J35" s="26">
@@ -24545,28 +24561,28 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G36" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I36" s="26"/>
       <c r="J36" s="26">
@@ -24575,28 +24591,28 @@
     </row>
     <row r="37" spans="1:10" ht="64.5">
       <c r="A37" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I37" s="26"/>
       <c r="J37" s="26">
@@ -24605,24 +24621,24 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E38" s="26"/>
       <c r="F38" s="26"/>
       <c r="G38" s="26" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I38" s="26"/>
       <c r="J38" s="26">
@@ -24631,28 +24647,28 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I39" s="26"/>
       <c r="J39" s="26">
@@ -24661,31 +24677,31 @@
     </row>
     <row r="40" spans="1:10" ht="64.5">
       <c r="A40" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E40" s="35" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="J40" s="26">
         <v>34</v>
@@ -24693,28 +24709,28 @@
     </row>
     <row r="41" spans="1:10" ht="179.25">
       <c r="A41" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E41" s="35" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I41" s="26"/>
       <c r="J41" s="26">
@@ -24723,28 +24739,28 @@
     </row>
     <row r="42" spans="1:10" ht="204.75">
       <c r="A42" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E42" s="35" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I42" s="26"/>
       <c r="J42" s="26">
@@ -24753,28 +24769,28 @@
     </row>
     <row r="43" spans="1:10" ht="64.5">
       <c r="A43" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E43" s="35" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I43" s="26"/>
       <c r="J43" s="26">
@@ -24783,31 +24799,31 @@
     </row>
     <row r="44" spans="1:10" ht="166.5">
       <c r="A44" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H44" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I44" s="26" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="J44" s="26">
         <v>77</v>
@@ -24815,28 +24831,28 @@
     </row>
     <row r="45" spans="1:10" ht="141">
       <c r="A45" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H45" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I45" s="26"/>
       <c r="J45" s="26">
@@ -24845,28 +24861,28 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I46" s="26"/>
       <c r="J46" s="26">
@@ -24875,28 +24891,28 @@
     </row>
     <row r="47" spans="1:10" ht="255.75">
       <c r="A47" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G47" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I47" s="26"/>
       <c r="J47" s="26">
@@ -24905,28 +24921,28 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>91</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I48" s="26"/>
       <c r="J48" s="26">
@@ -24935,26 +24951,26 @@
     </row>
     <row r="49" spans="1:10" ht="153.75">
       <c r="A49" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E49" s="35" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="F49" s="26"/>
       <c r="G49" s="26" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I49" s="26"/>
       <c r="J49" s="26">
@@ -24963,28 +24979,28 @@
     </row>
     <row r="50" spans="1:10" ht="153.75">
       <c r="A50" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I50" s="26"/>
       <c r="J50" s="26">
@@ -24993,28 +25009,28 @@
     </row>
     <row r="51" spans="1:10" ht="102.75">
       <c r="A51" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E51" s="35" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G51" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H51" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I51" s="26"/>
       <c r="J51" s="26">
@@ -25023,26 +25039,26 @@
     </row>
     <row r="52" spans="1:10" ht="345">
       <c r="A52" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="F52" s="26"/>
       <c r="G52" s="26" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I52" s="26"/>
       <c r="J52" s="26">
@@ -25051,26 +25067,26 @@
     </row>
     <row r="53" spans="1:10" ht="204.75">
       <c r="A53" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E53" s="35" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="F53" s="26"/>
       <c r="G53" s="26" t="s">
         <v>91</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I53" s="26"/>
       <c r="J53" s="26">
@@ -25079,28 +25095,28 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I54" s="26"/>
       <c r="J54" s="26">
@@ -25109,28 +25125,28 @@
     </row>
     <row r="55" spans="1:10" ht="64.5">
       <c r="A55" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D55" s="26" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E55" s="35" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I55" s="26"/>
       <c r="J55" s="26">
@@ -25139,28 +25155,28 @@
     </row>
     <row r="56" spans="1:10" ht="179.25">
       <c r="A56" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H56" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I56" s="26"/>
       <c r="J56" s="26">
@@ -25169,26 +25185,26 @@
     </row>
     <row r="57" spans="1:10" ht="166.5">
       <c r="A57" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E57" s="35" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="F57" s="26"/>
       <c r="G57" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H57" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I57" s="26"/>
       <c r="J57" s="26">
@@ -25197,26 +25213,26 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E58" s="26"/>
       <c r="F58" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H58" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I58" s="26"/>
       <c r="J58" s="26">
@@ -25225,28 +25241,28 @@
     </row>
     <row r="59" spans="1:10" ht="77.25">
       <c r="A59" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E59" s="35" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G59" s="26" t="s">
         <v>91</v>
       </c>
       <c r="H59" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I59" s="26"/>
       <c r="J59" s="26">
@@ -25255,28 +25271,28 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G60" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I60" s="26"/>
       <c r="J60" s="26">
@@ -25285,28 +25301,28 @@
     </row>
     <row r="61" spans="1:10" ht="115.5">
       <c r="A61" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="E61" s="35" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>91</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I61" s="26"/>
       <c r="J61" s="26">
@@ -25315,28 +25331,28 @@
     </row>
     <row r="62" spans="1:10" ht="243">
       <c r="A62" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G62" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I62" s="26"/>
       <c r="J62" s="26">
@@ -25345,10 +25361,10 @@
     </row>
     <row r="63" spans="1:10" ht="39">
       <c r="A63" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C63" s="26" t="s">
         <v>45</v>
@@ -25357,16 +25373,16 @@
         <v>46</v>
       </c>
       <c r="E63" s="35" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H63" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I63" s="26"/>
       <c r="J63" s="26">
@@ -25375,28 +25391,28 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G64" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H64" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I64" s="26"/>
       <c r="J64" s="26">
@@ -25405,28 +25421,28 @@
     </row>
     <row r="65" spans="1:10" ht="39">
       <c r="A65" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E65" s="35" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H65" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I65" s="26"/>
       <c r="J65" s="26">
@@ -25435,26 +25451,26 @@
     </row>
     <row r="66" spans="1:10" ht="77.25">
       <c r="A66" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E66" s="35" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="F66" s="26"/>
       <c r="G66" s="26" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I66" s="26"/>
       <c r="J66" s="26">
@@ -25463,28 +25479,28 @@
     </row>
     <row r="67" spans="1:10" ht="77.25">
       <c r="A67" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E67" s="35" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H67" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I67" s="26"/>
       <c r="J67" s="26">
@@ -25493,28 +25509,28 @@
     </row>
     <row r="68" spans="1:10" ht="243">
       <c r="A68" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E68" s="35" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H68" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I68" s="26"/>
       <c r="J68" s="26">
@@ -25523,28 +25539,28 @@
     </row>
     <row r="69" spans="1:10" ht="51.75">
       <c r="A69" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E69" s="35" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H69" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I69" s="26"/>
       <c r="J69" s="26">
@@ -25553,28 +25569,28 @@
     </row>
     <row r="70" spans="1:10" ht="153.75">
       <c r="A70" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E70" s="35" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I70" s="26"/>
       <c r="J70" s="26">
@@ -25583,28 +25599,28 @@
     </row>
     <row r="71" spans="1:10" ht="141">
       <c r="A71" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E71" s="35" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I71" s="26"/>
       <c r="J71" s="26">
@@ -25613,26 +25629,26 @@
     </row>
     <row r="72" spans="1:10" ht="153.75">
       <c r="A72" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E72" s="35" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="F72" s="26"/>
       <c r="G72" s="26" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I72" s="26"/>
       <c r="J72" s="26">
@@ -25641,28 +25657,28 @@
     </row>
     <row r="73" spans="1:10" ht="102.75">
       <c r="A73" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E73" s="35" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H73" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I73" s="26"/>
       <c r="J73" s="26">
@@ -25671,28 +25687,28 @@
     </row>
     <row r="74" spans="1:10" ht="39">
       <c r="A74" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E74" s="35" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I74" s="26"/>
       <c r="J74" s="26">
@@ -25701,10 +25717,10 @@
     </row>
     <row r="75" spans="1:10" ht="39">
       <c r="A75" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C75" s="26" t="s">
         <v>75</v>
@@ -25713,16 +25729,16 @@
         <v>76</v>
       </c>
       <c r="E75" s="35" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>77</v>
       </c>
       <c r="H75" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I75" s="26"/>
       <c r="J75" s="26">
@@ -25731,10 +25747,10 @@
     </row>
     <row r="76" spans="1:10" ht="39">
       <c r="A76" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C76" s="26" t="s">
         <v>86</v>
@@ -25743,16 +25759,16 @@
         <v>87</v>
       </c>
       <c r="E76" s="35" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H76" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I76" s="26"/>
       <c r="J76" s="26">
@@ -25761,10 +25777,10 @@
     </row>
     <row r="77" spans="1:10" ht="39">
       <c r="A77" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C77" s="26" t="s">
         <v>80</v>
@@ -25773,16 +25789,16 @@
         <v>81</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I77" s="26"/>
       <c r="J77" s="26">
@@ -25791,10 +25807,10 @@
     </row>
     <row r="78" spans="1:10" ht="26.25">
       <c r="A78" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C78" s="26" t="s">
         <v>83</v>
@@ -25803,16 +25819,16 @@
         <v>84</v>
       </c>
       <c r="E78" s="35" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H78" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I78" s="26"/>
       <c r="J78" s="26">
@@ -25821,28 +25837,28 @@
     </row>
     <row r="79" spans="1:10" ht="396">
       <c r="A79" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E79" s="35" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>101</v>
       </c>
       <c r="H79" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I79" s="26"/>
       <c r="J79" s="26">
@@ -25851,28 +25867,28 @@
     </row>
     <row r="80" spans="1:10" ht="26.25">
       <c r="A80" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E80" s="35" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="G80" s="26" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="H80" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I80" s="26"/>
       <c r="J80" s="26">
@@ -25881,29 +25897,29 @@
     </row>
     <row r="81" spans="1:10" ht="51.75">
       <c r="A81" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F81" s="26"/>
       <c r="G81" s="26" t="s">
         <v>91</v>
       </c>
       <c r="H81" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I81" s="26" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="J81" s="26">
         <v>51</v>
@@ -25911,28 +25927,28 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>41</v>
       </c>
       <c r="H82" s="26" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I82" s="26"/>
       <c r="J82" s="26">
@@ -25941,28 +25957,28 @@
     </row>
     <row r="83" spans="1:10" ht="51.75">
       <c r="A83" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E83" s="35" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="G83" s="26" t="s">
         <v>47</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I83" s="26"/>
       <c r="J83" s="26">
@@ -25971,28 +25987,28 @@
     </row>
     <row r="84" spans="1:10" ht="39">
       <c r="A84" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E84" s="35" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G84" s="26" t="s">
         <v>111</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I84" s="26"/>
       <c r="J84" s="26">
@@ -26001,28 +26017,28 @@
     </row>
     <row r="85" spans="1:10" ht="51.75">
       <c r="A85" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E85" s="35" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H85" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I85" s="26"/>
       <c r="J85" s="26">
@@ -26031,28 +26047,28 @@
     </row>
     <row r="86" spans="1:10" ht="39">
       <c r="A86" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D86" s="26" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E86" s="35" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G86" s="26" t="s">
         <v>101</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I86" s="26"/>
       <c r="J86" s="26">
@@ -26061,28 +26077,28 @@
     </row>
     <row r="87" spans="1:10" ht="51.75">
       <c r="A87" s="26" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D87" s="26" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="E87" s="35" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G87" s="26" t="s">
         <v>71</v>
       </c>
       <c r="H87" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I87" s="26"/>
       <c r="J87" s="26">
@@ -26312,30 +26328,30 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B1" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="C1" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="D1" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="E1" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="F1" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B2" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C2" t="s">
         <v>48</v>
@@ -26344,15 +26360,15 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B3" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C3" t="s">
         <v>48</v>
@@ -26361,7 +26377,7 @@
         <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -26369,7 +26385,7 @@
         <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
@@ -26378,12 +26394,12 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="B5" t="s">
         <v>41</v>
@@ -26395,12 +26411,12 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B6" t="s">
         <v>41</v>
@@ -26412,7 +26428,7 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -26420,7 +26436,7 @@
         <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
@@ -26429,7 +26445,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -26446,12 +26462,12 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -26463,7 +26479,7 @@
         <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -26480,15 +26496,15 @@
         <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C11" t="s">
         <v>48</v>
@@ -26497,12 +26513,12 @@
         <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
@@ -26514,7 +26530,7 @@
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -26531,15 +26547,15 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="B14" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C14" t="s">
         <v>48</v>
@@ -26548,7 +26564,7 @@
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -26565,15 +26581,15 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B16" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="C16" t="s">
         <v>48</v>
@@ -26582,7 +26598,7 @@
         <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -26599,12 +26615,12 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s">
         <v>111</v>
@@ -26616,15 +26632,15 @@
         <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C19" t="s">
         <v>48</v>
@@ -26633,15 +26649,15 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B20" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C20" t="s">
         <v>48</v>
@@ -26650,15 +26666,15 @@
         <v>82</v>
       </c>
       <c r="F20" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B21" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C21" t="s">
         <v>48</v>
@@ -26667,21 +26683,21 @@
         <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B22" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C22" t="s">
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E22" s="25">
         <v>65</v>
@@ -26689,30 +26705,30 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B23" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C23" t="s">
         <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E23" s="25">
         <v>66</v>
       </c>
       <c r="F23" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C24" t="s">
         <v>48</v>
@@ -26721,15 +26737,15 @@
         <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
@@ -26738,12 +26754,12 @@
         <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
         <v>111</v>
@@ -26755,15 +26771,15 @@
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B27" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C27" t="s">
         <v>48</v>
@@ -26772,7 +26788,7 @@
         <v>83</v>
       </c>
       <c r="F27" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -26789,12 +26805,12 @@
         <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -26806,7 +26822,7 @@
         <v>73</v>
       </c>
       <c r="F29" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -26823,12 +26839,12 @@
         <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
@@ -26840,12 +26856,12 @@
         <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
         <v>111</v>
@@ -26857,12 +26873,12 @@
         <v>28</v>
       </c>
       <c r="F32" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B33" t="s">
         <v>111</v>
@@ -26874,12 +26890,12 @@
         <v>29</v>
       </c>
       <c r="F33" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B34" t="s">
         <v>91</v>
@@ -26891,12 +26907,12 @@
         <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
@@ -26908,12 +26924,12 @@
         <v>76</v>
       </c>
       <c r="F35" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B36" t="s">
         <v>41</v>
@@ -26925,21 +26941,21 @@
         <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C37" t="s">
         <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="E37" s="25">
         <v>71</v>
@@ -26947,27 +26963,27 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C38" t="s">
         <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E38" s="25">
         <v>72</v>
       </c>
       <c r="F38" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B39" t="s">
         <v>111</v>
@@ -26979,15 +26995,15 @@
         <v>34</v>
       </c>
       <c r="F39" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C40" t="s">
         <v>48</v>
@@ -26996,15 +27012,15 @@
         <v>32</v>
       </c>
       <c r="F40" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C41" t="s">
         <v>48</v>
@@ -27013,15 +27029,15 @@
         <v>33</v>
       </c>
       <c r="F41" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B42" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C42" t="s">
         <v>48</v>
@@ -27030,15 +27046,15 @@
         <v>35</v>
       </c>
       <c r="F42" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B43" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C43" t="s">
         <v>48</v>
@@ -27047,12 +27063,12 @@
         <v>84</v>
       </c>
       <c r="F43" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s">
         <v>111</v>
@@ -27064,12 +27080,12 @@
         <v>37</v>
       </c>
       <c r="F44" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B45" t="s">
         <v>41</v>
@@ -27083,10 +27099,10 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B46" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C46" t="s">
         <v>48</v>
@@ -27095,15 +27111,15 @@
         <v>38</v>
       </c>
       <c r="F46" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B47" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C47" t="s">
         <v>48</v>
@@ -27112,12 +27128,12 @@
         <v>40</v>
       </c>
       <c r="F47" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
         <v>111</v>
@@ -27129,12 +27145,12 @@
         <v>41</v>
       </c>
       <c r="F48" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B49" t="s">
         <v>111</v>
@@ -27146,15 +27162,15 @@
         <v>42</v>
       </c>
       <c r="F49" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B50" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C50" t="s">
         <v>48</v>
@@ -27163,12 +27179,12 @@
         <v>43</v>
       </c>
       <c r="F50" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
         <v>91</v>
@@ -27180,12 +27196,12 @@
         <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B52" t="s">
         <v>41</v>
@@ -27197,12 +27213,12 @@
         <v>79</v>
       </c>
       <c r="F52" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B53" t="s">
         <v>111</v>
@@ -27214,12 +27230,12 @@
         <v>44</v>
       </c>
       <c r="F53" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B54" t="s">
         <v>111</v>
@@ -27231,15 +27247,15 @@
         <v>45</v>
       </c>
       <c r="F54" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B55" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C55" t="s">
         <v>48</v>
@@ -27248,12 +27264,12 @@
         <v>47</v>
       </c>
       <c r="F55" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B56" t="s">
         <v>111</v>
@@ -27265,12 +27281,12 @@
         <v>59</v>
       </c>
       <c r="F56" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B57" t="s">
         <v>111</v>
@@ -27282,12 +27298,12 @@
         <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s">
         <v>111</v>
@@ -27299,12 +27315,12 @@
         <v>58</v>
       </c>
       <c r="F58" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B59" t="s">
         <v>111</v>
@@ -27316,12 +27332,12 @@
         <v>60</v>
       </c>
       <c r="F59" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B60" t="s">
         <v>111</v>
@@ -27333,15 +27349,15 @@
         <v>61</v>
       </c>
       <c r="F60" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B61" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C61" t="s">
         <v>48</v>
@@ -27350,12 +27366,12 @@
         <v>63</v>
       </c>
       <c r="F61" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s">
         <v>111</v>
@@ -27367,12 +27383,12 @@
         <v>64</v>
       </c>
       <c r="F62" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B63" t="s">
         <v>111</v>
@@ -27384,12 +27400,12 @@
         <v>54</v>
       </c>
       <c r="F63" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B64" t="s">
         <v>91</v>
@@ -27401,12 +27417,12 @@
         <v>48</v>
       </c>
       <c r="F64" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="B65" t="s">
         <v>41</v>
@@ -27418,12 +27434,12 @@
         <v>77</v>
       </c>
       <c r="F65" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B66" t="s">
         <v>41</v>
@@ -27437,7 +27453,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="B67" t="s">
         <v>91</v>
@@ -27449,15 +27465,15 @@
         <v>49</v>
       </c>
       <c r="F67" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B68" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C68" t="s">
         <v>48</v>
@@ -27466,7 +27482,7 @@
         <v>46</v>
       </c>
       <c r="F68" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -27474,7 +27490,7 @@
         <v>46</v>
       </c>
       <c r="B69" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C69" t="s">
         <v>48</v>
@@ -27483,12 +27499,12 @@
         <v>2</v>
       </c>
       <c r="F69" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B70" t="s">
         <v>41</v>
@@ -27500,12 +27516,12 @@
         <v>80</v>
       </c>
       <c r="F70" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B71" t="s">
         <v>41</v>
@@ -27517,15 +27533,15 @@
         <v>68</v>
       </c>
       <c r="F71" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B72" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="C72" t="s">
         <v>48</v>
@@ -27534,7 +27550,7 @@
         <v>69</v>
       </c>
       <c r="F72" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -27542,7 +27558,7 @@
         <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C73" t="s">
         <v>48</v>
@@ -27551,7 +27567,7 @@
         <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -27568,7 +27584,7 @@
         <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -27576,7 +27592,7 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C75" t="s">
         <v>48</v>
@@ -27585,7 +27601,7 @@
         <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -27602,15 +27618,15 @@
         <v>11</v>
       </c>
       <c r="F76" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B77" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C77" t="s">
         <v>48</v>
@@ -27619,15 +27635,15 @@
         <v>81</v>
       </c>
       <c r="F77" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B78" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C78" t="s">
         <v>48</v>
@@ -27636,12 +27652,12 @@
         <v>50</v>
       </c>
       <c r="F78" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B79" t="s">
         <v>91</v>
@@ -27653,12 +27669,12 @@
         <v>51</v>
       </c>
       <c r="F79" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s">
         <v>41</v>
@@ -27670,15 +27686,15 @@
         <v>78</v>
       </c>
       <c r="F80" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B81" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C81" t="s">
         <v>48</v>
@@ -27687,12 +27703,12 @@
         <v>52</v>
       </c>
       <c r="F81" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B82" t="s">
         <v>111</v>
@@ -27704,15 +27720,15 @@
         <v>53</v>
       </c>
       <c r="F82" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B83" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C83" t="s">
         <v>48</v>
@@ -27721,15 +27737,15 @@
         <v>55</v>
       </c>
       <c r="F83" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B84" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C84" t="s">
         <v>48</v>
@@ -27738,15 +27754,15 @@
         <v>57</v>
       </c>
       <c r="F84" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B85" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C85" t="s">
         <v>48</v>
@@ -27755,7 +27771,7 @@
         <v>56</v>
       </c>
       <c r="F85" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -27767,6 +27783,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="58a27bba-3e67-43d1-8504-e8ab049072dd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8889ac66-a331-4fe6-8d0f-c6fea2346e24">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="58a27bba-3e67-43d1-8504-e8ab049072dd">
+      <UserInfo>
+        <DisplayName>Anand Waishampayan</DisplayName>
+        <AccountId>70</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100689FE176A865024B82746AC01372DAB6" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="922c480ddc59e6305a8a8fb3a8148c08">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8889ac66-a331-4fe6-8d0f-c6fea2346e24" xmlns:ns3="58a27bba-3e67-43d1-8504-e8ab049072dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7adf1aec20f105c257528873c177ef16" ns2:_="" ns3:_="">
     <xsd:import namespace="8889ac66-a331-4fe6-8d0f-c6fea2346e24"/>
@@ -28015,41 +28058,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="58a27bba-3e67-43d1-8504-e8ab049072dd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8889ac66-a331-4fe6-8d0f-c6fea2346e24">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="58a27bba-3e67-43d1-8504-e8ab049072dd">
-      <UserInfo>
-        <DisplayName>Anand Waishampayan</DisplayName>
-        <AccountId>70</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC84F7F3-77E9-4523-AFE1-BA9C3C1DDAE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BB92FD7-3D67-4D76-9D89-2FC79341A64F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="58a27bba-3e67-43d1-8504-e8ab049072dd"/>
+    <ds:schemaRef ds:uri="8889ac66-a331-4fe6-8d0f-c6fea2346e24"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BB92FD7-3D67-4D76-9D89-2FC79341A64F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1E513F4-A103-415D-B9AD-2F9B0BEDFF36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1E513F4-A103-415D-B9AD-2F9B0BEDFF36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC84F7F3-77E9-4523-AFE1-BA9C3C1DDAE8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8889ac66-a331-4fe6-8d0f-c6fea2346e24"/>
+    <ds:schemaRef ds:uri="58a27bba-3e67-43d1-8504-e8ab049072dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>